--- a/docs/exports/P38-eletrica-benchmark-lm.xlsx
+++ b/docs/exports/P38-eletrica-benchmark-lm.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3211" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3211" uniqueCount="567">
   <si>
     <t>métrica</t>
   </si>
@@ -63,10 +63,10 @@
     <t>Trabalhamos somente com fio flexível; hits legado FIO ELÉTRICO contam como tem até renomear SKU.</t>
   </si>
   <si>
-    <t>Ecossistema DIN</t>
-  </si>
-  <si>
-    <t>Trilho DIN 35mm, barramentos, DR/IDR e DPS alinhados ao sistema modular dos quadros plásticos Tigre (já no cadastro). Krona: compatível trilho 35mm padrão. Quadro metálico Steck: trilho DIN universal — mesma bitola 35mm.</t>
+    <t>Sistema DIN</t>
+  </si>
+  <si>
+    <t>Trilho DIN 35mm, barramentos, DR/IDR e DPS no mesmo sistema modular dos quadros. Marca não travada — escolher boa marca compatível DIN na compra.</t>
   </si>
   <si>
     <t>06 — Padrão de entrada</t>
@@ -462,7 +462,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>QUADRO DE DISTRIBUIÇÃO 8 DISJUNTORES — TIGRE</t>
+    <t>QUADRO DE DISTRIBUIÇÃO 8 DISJUNTORES PLÁSTICO</t>
   </si>
   <si>
     <t>Quadros e Complementos &gt; Plástico (sobrepor/embutir)</t>
@@ -471,7 +471,7 @@
     <t>https://www.leroymerlin.com.br/quadros-de-distribuicao</t>
   </si>
   <si>
-    <t>Plástico Tigre — ecossistema DIN (trilho/barramento/DR/DPS mesma linha)</t>
+    <t>Plástico — boa marca; compatível trilho DIN 35mm</t>
   </si>
   <si>
     <t>12 disjuntores — plástico</t>
@@ -489,7 +489,7 @@
     <t>QUADRO DE DISTRIBUIÇAO 12/16 - TIGRE</t>
   </si>
   <si>
-    <t>Plástico Tigre/Krona — ecossistema DIN TIGRE · revisar marca (Trial no cadastro)</t>
+    <t>Plástico — boa marca; compatível trilho DIN 35mm · cadastro legado — revisar marca na próxima compra</t>
   </si>
   <si>
     <t>16 disjuntores — plástico</t>
@@ -507,9 +507,6 @@
     <t>QUADRO DE DISTRIBUIÇÃO 16 - KRONA</t>
   </si>
   <si>
-    <t>Plástico Tigre/Krona — ecossistema DIN TIGRE</t>
-  </si>
-  <si>
     <t>quadro_metalico</t>
   </si>
   <si>
@@ -519,28 +516,25 @@
     <t>8 disjuntores — metálico</t>
   </si>
   <si>
-    <t>QUADRO METÁLICO DE DISJUNTORES 8 — STECK</t>
+    <t>QUADRO METÁLICO DE DISJUNTORES 8</t>
   </si>
   <si>
     <t>Quadros e Complementos &gt; Metálico</t>
   </si>
   <si>
-    <t>Metálico — marca referência Steck (alternativa Schneider)</t>
+    <t>Metálico — boa marca</t>
   </si>
   <si>
     <t>12 disjuntores — metálico</t>
   </si>
   <si>
-    <t>QUADRO METÁLICO DE DISJUNTORES 12 — STECK</t>
-  </si>
-  <si>
-    <t>Metálico — marca referência Steck</t>
+    <t>QUADRO METÁLICO DE DISJUNTORES 12</t>
   </si>
   <si>
     <t>16 disjuntores — metálico</t>
   </si>
   <si>
-    <t>QUADRO METÁLICO DE DISJUNTORES 16 — STECK</t>
+    <t>QUADRO METÁLICO DE DISJUNTORES 16</t>
   </si>
   <si>
     <t>montagem_din</t>
@@ -555,7 +549,7 @@
     <t>35MM 1M</t>
   </si>
   <si>
-    <t>TRILHO DIN 35MM 1M — TIGRE</t>
+    <t>TRILHO DIN 35MM 1M</t>
   </si>
   <si>
     <t>Quadros &gt; Trilho DIN e barramentos</t>
@@ -564,7 +558,7 @@
     <t>https://www.leroymerlin.com.br/trilho-din</t>
   </si>
   <si>
-    <t>Base montagem modular — ecossistema quadro Tigre</t>
+    <t>Base montagem modular — boa marca</t>
   </si>
   <si>
     <t>Trilho DIN 35mm 2m</t>
@@ -573,16 +567,16 @@
     <t>35MM 2M</t>
   </si>
   <si>
-    <t>TRILHO DIN 35MM 2M — TIGRE</t>
-  </si>
-  <si>
-    <t>Trilho/barramento TIGRE — par quadros plásticos</t>
+    <t>TRILHO DIN 35MM 2M</t>
+  </si>
+  <si>
+    <t>boa marca — sistema DIN 35mm compatível com quadros</t>
   </si>
   <si>
     <t>Barramento neutro 12 polos</t>
   </si>
   <si>
-    <t>BARRAMENTO NEUTRO 12 POLOS — TIGRE</t>
+    <t>BARRAMENTO NEUTRO 12 POLOS</t>
   </si>
   <si>
     <t>Par com quadro 12 disj. plástico</t>
@@ -594,7 +588,7 @@
     <t>16 POLOS</t>
   </si>
   <si>
-    <t>BARRAMENTO NEUTRO 16 POLOS — TIGRE</t>
+    <t>BARRAMENTO NEUTRO 16 POLOS</t>
   </si>
   <si>
     <t>Par com quadro 16 disj.</t>
@@ -603,13 +597,13 @@
     <t>Barramento terra 12 polos</t>
   </si>
   <si>
-    <t>BARRAMENTO TERRA 12 POLOS — TIGRE</t>
+    <t>BARRAMENTO TERRA 12 POLOS</t>
   </si>
   <si>
     <t>Barramento terra 16 polos</t>
   </si>
   <si>
-    <t>BARRAMENTO TERRA 16 POLOS — TIGRE</t>
+    <t>BARRAMENTO TERRA 16 POLOS</t>
   </si>
   <si>
     <t>dr_idr</t>
@@ -621,7 +615,7 @@
     <t>2P</t>
   </si>
   <si>
-    <t>DR 25A 2P — TIGRE</t>
+    <t>DR 25A 2P</t>
   </si>
   <si>
     <t>Proteção &gt; DR / IDR</t>
@@ -633,19 +627,19 @@
     <t>IDR residencial — chuveiro/tomadas</t>
   </si>
   <si>
-    <t>DR 40A 2P — TIGRE</t>
-  </si>
-  <si>
-    <t>Ecossistema DIN TIGRE</t>
-  </si>
-  <si>
-    <t>DR 63A 2P — TIGRE</t>
+    <t>DR 40A 2P</t>
+  </si>
+  <si>
+    <t>boa marca — modular DIN</t>
+  </si>
+  <si>
+    <t>DR 63A 2P</t>
   </si>
   <si>
     <t>4P</t>
   </si>
   <si>
-    <t>DR 40A 4P — TIGRE</t>
+    <t>DR 40A 4P</t>
   </si>
   <si>
     <t>Trifásico + neutro</t>
@@ -663,7 +657,7 @@
     <t>2P 20KA</t>
   </si>
   <si>
-    <t>DPS 20KA 2P CLASSE II — TIGRE</t>
+    <t>DPS 20KA 2P CLASSE II</t>
   </si>
   <si>
     <t>Proteção &gt; DPS (surto)</t>
@@ -681,7 +675,7 @@
     <t>4P 40KA</t>
   </si>
   <si>
-    <t>DPS 40KA 4P CLASSE II — TIGRE</t>
+    <t>DPS 40KA 4P CLASSE II</t>
   </si>
   <si>
     <t>Entrada trifásica / projeto</t>
@@ -1053,7 +1047,7 @@
     <t>1"</t>
   </si>
   <si>
-    <t>CONDUITE CORRUGADO 1" TRAMONTINA</t>
+    <t>CONDUITE CORRUGADO 1"</t>
   </si>
   <si>
     <t>eletroduto_kit</t>
@@ -1095,7 +1089,7 @@
     <t>Bucha 1¼"</t>
   </si>
   <si>
-    <t>BUCHA ELETRODUTO 1 1/4' INCA</t>
+    <t>BUCHA ELETRODUTO 1 1/4'</t>
   </si>
   <si>
     <t>Eletrodutos &gt; Buchas</t>
@@ -1276,9 +1270,6 @@
   </si>
   <si>
     <t>secao</t>
-  </si>
-  <si>
-    <t>TIGRE</t>
   </si>
   <si>
     <t>BARRAMENTO NEUTRO</t>
@@ -2340,19 +2331,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>36</v>
@@ -2712,22 +2703,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D1" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="E1" s="11" t="s">
-        <v>398</v>
-      </c>
       <c r="F1" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2735,19 +2726,19 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" t="s">
         <v>239</v>
-      </c>
-      <c r="D2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2755,19 +2746,19 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" t="s">
         <v>232</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" t="s">
         <v>234</v>
-      </c>
-      <c r="D3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2775,19 +2766,19 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F4" t="s">
         <v>243</v>
-      </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2795,7 +2786,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C5" t="s">
         <v>41</v>
@@ -2804,10 +2795,10 @@
         <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2815,19 +2806,19 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6" t="s">
         <v>252</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2835,19 +2826,19 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
         <v>247</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>248</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2855,19 +2846,19 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" t="s">
         <v>255</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>256</v>
-      </c>
-      <c r="F8" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2875,19 +2866,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C9" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D9" t="s">
         <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2895,19 +2886,19 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" t="s">
         <v>259</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>260</v>
+      </c>
+      <c r="F10" t="s">
         <v>261</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>262</v>
-      </c>
-      <c r="F10" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2915,19 +2906,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C11" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" t="s">
         <v>266</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>267</v>
-      </c>
-      <c r="F11" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2935,19 +2926,19 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C12" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2955,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C13" t="s">
         <v>43</v>
@@ -2964,10 +2955,10 @@
         <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2975,7 +2966,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
@@ -2984,698 +2975,698 @@
         <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>428</v>
+      </c>
+      <c r="B15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C15" t="s">
+        <v>349</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>430</v>
+      </c>
+      <c r="F15" t="s">
         <v>431</v>
-      </c>
-      <c r="B15" t="s">
-        <v>432</v>
-      </c>
-      <c r="C15" t="s">
-        <v>351</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" t="s">
-        <v>433</v>
-      </c>
-      <c r="F15" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B16" t="s">
+        <v>429</v>
+      </c>
+      <c r="C16" t="s">
+        <v>330</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
         <v>432</v>
       </c>
-      <c r="C16" t="s">
-        <v>332</v>
-      </c>
-      <c r="D16" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" t="s">
-        <v>435</v>
-      </c>
       <c r="F16" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C17" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F17" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B18" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C18" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D18" t="s">
         <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F18" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B19" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C19" t="s">
+        <v>439</v>
+      </c>
+      <c r="D19" t="s">
+        <v>440</v>
+      </c>
+      <c r="E19" t="s">
+        <v>441</v>
+      </c>
+      <c r="F19" t="s">
         <v>442</v>
-      </c>
-      <c r="D19" t="s">
-        <v>443</v>
-      </c>
-      <c r="E19" t="s">
-        <v>444</v>
-      </c>
-      <c r="F19" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D20" t="s">
+        <v>440</v>
+      </c>
+      <c r="E20" t="s">
         <v>443</v>
       </c>
-      <c r="E20" t="s">
-        <v>446</v>
-      </c>
       <c r="F20" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B21" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C21" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D21" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E21" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F21" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B22" t="s">
+        <v>447</v>
+      </c>
+      <c r="C22" t="s">
+        <v>448</v>
+      </c>
+      <c r="D22" t="s">
+        <v>449</v>
+      </c>
+      <c r="E22" t="s">
         <v>450</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
         <v>451</v>
-      </c>
-      <c r="D22" t="s">
-        <v>452</v>
-      </c>
-      <c r="E22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F22" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B23" t="s">
+        <v>365</v>
+      </c>
+      <c r="C23" t="s">
+        <v>452</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
         <v>367</v>
       </c>
-      <c r="C23" t="s">
-        <v>455</v>
-      </c>
-      <c r="D23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" t="s">
-        <v>369</v>
-      </c>
       <c r="F23" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B24" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24" t="s">
         <v>330</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>453</v>
+      </c>
+      <c r="E24" t="s">
+        <v>331</v>
+      </c>
+      <c r="F24" t="s">
         <v>332</v>
-      </c>
-      <c r="D24" t="s">
-        <v>456</v>
-      </c>
-      <c r="E24" t="s">
-        <v>333</v>
-      </c>
-      <c r="F24" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B25" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C25" t="s">
+        <v>336</v>
+      </c>
+      <c r="D25" t="s">
+        <v>453</v>
+      </c>
+      <c r="E25" t="s">
+        <v>337</v>
+      </c>
+      <c r="F25" t="s">
         <v>338</v>
-      </c>
-      <c r="D25" t="s">
-        <v>456</v>
-      </c>
-      <c r="E25" t="s">
-        <v>339</v>
-      </c>
-      <c r="F25" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B26" t="s">
+        <v>454</v>
+      </c>
+      <c r="C26" t="s">
+        <v>455</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>456</v>
+      </c>
+      <c r="F26" t="s">
         <v>457</v>
-      </c>
-      <c r="C26" t="s">
-        <v>458</v>
-      </c>
-      <c r="D26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" t="s">
-        <v>459</v>
-      </c>
-      <c r="F26" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B27" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C27" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D27" t="s">
         <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F27" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B28" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C28" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D28" t="s">
         <v>43</v>
       </c>
       <c r="E28" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F28" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B29" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D29" t="s">
         <v>43</v>
       </c>
       <c r="E29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F29" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B30" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C30" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D30" t="s">
         <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F30" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B31" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C31" t="s">
         <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E31" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B32" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C32" t="s">
         <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E32" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F32" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B33" t="s">
+        <v>466</v>
+      </c>
+      <c r="C33" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" t="s">
         <v>469</v>
       </c>
-      <c r="C33" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" t="s">
-        <v>472</v>
-      </c>
       <c r="E33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F33" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B34" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C34" t="s">
         <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E34" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F34" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B35" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C35" t="s">
         <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E35" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F35" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B36" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C36" t="s">
         <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E36" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F36" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B37" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C37" t="s">
         <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E37" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F37" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B38" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C38" t="s">
         <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E38" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F38" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B39" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C39" t="s">
         <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F39" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B40" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C40" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D40" t="s">
         <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F40" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B41" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C41" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D41" t="s">
         <v>43</v>
       </c>
       <c r="E41" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F41" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B42" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C42" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D42" t="s">
         <v>43</v>
       </c>
       <c r="E42" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F42" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B43" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C43" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D43" t="s">
         <v>43</v>
       </c>
       <c r="E43" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F43" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s">
+        <v>487</v>
+      </c>
+      <c r="C44" t="s">
+        <v>488</v>
+      </c>
+      <c r="D44" t="s">
+        <v>434</v>
+      </c>
+      <c r="E44" t="s">
+        <v>489</v>
+      </c>
+      <c r="F44" t="s">
         <v>490</v>
-      </c>
-      <c r="C44" t="s">
-        <v>491</v>
-      </c>
-      <c r="D44" t="s">
-        <v>437</v>
-      </c>
-      <c r="E44" t="s">
-        <v>492</v>
-      </c>
-      <c r="F44" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C45" t="s">
+        <v>488</v>
+      </c>
+      <c r="D45" t="s">
+        <v>455</v>
+      </c>
+      <c r="E45" t="s">
         <v>491</v>
       </c>
-      <c r="D45" t="s">
-        <v>458</v>
-      </c>
-      <c r="E45" t="s">
-        <v>494</v>
-      </c>
       <c r="F45" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C46" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D46" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E46" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F46" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B47" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C47" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D47" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E47" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F47" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D48" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E48" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F48" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B49" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C49" t="s">
         <v>43</v>
@@ -3684,38 +3675,38 @@
         <v>43</v>
       </c>
       <c r="E49" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F49" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s">
+        <v>499</v>
+      </c>
+      <c r="C50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" t="s">
         <v>502</v>
       </c>
-      <c r="C50" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" t="s">
-        <v>43</v>
-      </c>
-      <c r="E50" t="s">
-        <v>505</v>
-      </c>
       <c r="F50" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B51" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C51" t="s">
         <v>43</v>
@@ -3724,18 +3715,18 @@
         <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F51" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C52" t="s">
         <v>43</v>
@@ -3744,18 +3735,18 @@
         <v>43</v>
       </c>
       <c r="E52" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F52" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B53" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C53" t="s">
         <v>43</v>
@@ -3764,110 +3755,110 @@
         <v>43</v>
       </c>
       <c r="E53" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F53" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B54" t="s">
+        <v>510</v>
+      </c>
+      <c r="C54" t="s">
+        <v>511</v>
+      </c>
+      <c r="D54" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" t="s">
+        <v>512</v>
+      </c>
+      <c r="F54" t="s">
         <v>513</v>
-      </c>
-      <c r="C54" t="s">
-        <v>514</v>
-      </c>
-      <c r="D54" t="s">
-        <v>43</v>
-      </c>
-      <c r="E54" t="s">
-        <v>515</v>
-      </c>
-      <c r="F54" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C55" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D55" t="s">
         <v>43</v>
       </c>
       <c r="E55" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F55" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C56" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D56" t="s">
         <v>43</v>
       </c>
       <c r="E56" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F56" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C57" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D57" t="s">
         <v>43</v>
       </c>
       <c r="E57" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F57" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C58" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D58" t="s">
         <v>43</v>
       </c>
       <c r="E58" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F58" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,13 +3869,13 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D59" t="s">
         <v>60</v>
       </c>
       <c r="E59" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F59" t="s">
         <v>61</v>
@@ -3898,13 +3889,13 @@
         <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D60" t="s">
         <v>60</v>
       </c>
       <c r="E60" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F60" t="s">
         <v>63</v>
@@ -3918,13 +3909,13 @@
         <v>39</v>
       </c>
       <c r="C61" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D61" t="s">
         <v>60</v>
       </c>
       <c r="E61" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F61" t="s">
         <v>64</v>
@@ -3938,13 +3929,13 @@
         <v>39</v>
       </c>
       <c r="C62" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D62" t="s">
         <v>60</v>
       </c>
       <c r="E62" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F62" t="s">
         <v>66</v>
@@ -3958,13 +3949,13 @@
         <v>39</v>
       </c>
       <c r="C63" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D63" t="s">
         <v>40</v>
       </c>
       <c r="E63" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F63" t="s">
         <v>44</v>
@@ -3978,13 +3969,13 @@
         <v>39</v>
       </c>
       <c r="C64" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D64" t="s">
         <v>40</v>
       </c>
       <c r="E64" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F64" t="s">
         <v>53</v>
@@ -3998,13 +3989,13 @@
         <v>39</v>
       </c>
       <c r="C65" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D65" t="s">
         <v>40</v>
       </c>
       <c r="E65" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F65" t="s">
         <v>55</v>
@@ -4018,13 +4009,13 @@
         <v>39</v>
       </c>
       <c r="C66" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D66" t="s">
         <v>40</v>
       </c>
       <c r="E66" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F66" t="s">
         <v>55</v>
@@ -4038,13 +4029,13 @@
         <v>39</v>
       </c>
       <c r="C67" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D67" t="s">
         <v>40</v>
       </c>
       <c r="E67" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F67" t="s">
         <v>57</v>
@@ -4058,13 +4049,13 @@
         <v>39</v>
       </c>
       <c r="C68" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D68" t="s">
         <v>40</v>
       </c>
       <c r="E68" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F68" t="s">
         <v>59</v>
@@ -4078,13 +4069,13 @@
         <v>143</v>
       </c>
       <c r="C69" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D69" t="s">
         <v>43</v>
       </c>
       <c r="E69" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F69" t="s">
         <v>154</v>
@@ -4104,10 +4095,10 @@
         <v>43</v>
       </c>
       <c r="E70" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F70" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4124,10 +4115,10 @@
         <v>43</v>
       </c>
       <c r="E71" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F71" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4158,16 +4149,16 @@
         <v>143</v>
       </c>
       <c r="C73" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D73" t="s">
         <v>43</v>
       </c>
       <c r="E73" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F73" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4178,16 +4169,16 @@
         <v>143</v>
       </c>
       <c r="C74" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D74" t="s">
         <v>43</v>
       </c>
       <c r="E74" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F74" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4195,19 +4186,19 @@
         <v>21</v>
       </c>
       <c r="B75" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C75" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D75" t="s">
         <v>43</v>
       </c>
       <c r="E75" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F75" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4215,7 +4206,7 @@
         <v>21</v>
       </c>
       <c r="B76" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C76" t="s">
         <v>43</v>
@@ -4224,10 +4215,10 @@
         <v>43</v>
       </c>
       <c r="E76" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F76" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4235,19 +4226,19 @@
         <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C77" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D77" t="s">
         <v>43</v>
       </c>
       <c r="E77" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F77" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4255,19 +4246,19 @@
         <v>21</v>
       </c>
       <c r="B78" t="s">
+        <v>371</v>
+      </c>
+      <c r="C78" t="s">
         <v>373</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
+        <v>43</v>
+      </c>
+      <c r="E78" t="s">
+        <v>374</v>
+      </c>
+      <c r="F78" t="s">
         <v>375</v>
-      </c>
-      <c r="D78" t="s">
-        <v>43</v>
-      </c>
-      <c r="E78" t="s">
-        <v>376</v>
-      </c>
-      <c r="F78" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4275,19 +4266,19 @@
         <v>21</v>
       </c>
       <c r="B79" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C79" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D79" t="s">
         <v>43</v>
       </c>
       <c r="E79" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F79" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,19 +4286,19 @@
         <v>21</v>
       </c>
       <c r="B80" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C80" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D80" t="s">
         <v>43</v>
       </c>
       <c r="E80" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F80" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,19 +4306,19 @@
         <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C81" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D81" t="s">
         <v>43</v>
       </c>
       <c r="E81" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F81" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,19 +4326,19 @@
         <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C82" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D82" t="s">
         <v>43</v>
       </c>
       <c r="E82" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F82" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -4355,19 +4346,19 @@
         <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C83" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D83" t="s">
         <v>43</v>
       </c>
       <c r="E83" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F83" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -4387,10 +4378,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>34</v>
@@ -4398,112 +4389,112 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B8" t="s">
         <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B9" t="s">
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B10" t="s">
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B11" t="s">
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -6402,7 +6393,7 @@
         <v>148</v>
       </c>
       <c r="L40" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="M40" t="s">
         <v>47</v>
@@ -6419,13 +6410,13 @@
         <v>19</v>
       </c>
       <c r="B41" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" t="s">
         <v>162</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>163</v>
-      </c>
-      <c r="D41" t="s">
-        <v>164</v>
       </c>
       <c r="E41" t="s">
         <v>145</v>
@@ -6440,16 +6431,16 @@
         <v>43</v>
       </c>
       <c r="I41" t="s">
+        <v>164</v>
+      </c>
+      <c r="J41" t="s">
         <v>165</v>
-      </c>
-      <c r="J41" t="s">
-        <v>166</v>
       </c>
       <c r="K41" t="s">
         <v>148</v>
       </c>
       <c r="L41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M41" t="s">
         <v>47</v>
@@ -6466,13 +6457,13 @@
         <v>19</v>
       </c>
       <c r="B42" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" t="s">
         <v>162</v>
       </c>
-      <c r="C42" t="s">
-        <v>163</v>
-      </c>
       <c r="D42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E42" t="s">
         <v>151</v>
@@ -6487,16 +6478,16 @@
         <v>43</v>
       </c>
       <c r="I42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K42" t="s">
         <v>148</v>
       </c>
       <c r="L42" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="M42" t="s">
         <v>47</v>
@@ -6513,13 +6504,13 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" t="s">
         <v>162</v>
       </c>
-      <c r="C43" t="s">
-        <v>163</v>
-      </c>
       <c r="D43" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E43" t="s">
         <v>157</v>
@@ -6534,16 +6525,16 @@
         <v>43</v>
       </c>
       <c r="I43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K43" t="s">
         <v>148</v>
       </c>
       <c r="L43" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="M43" t="s">
         <v>47</v>
@@ -6560,16 +6551,16 @@
         <v>19</v>
       </c>
       <c r="B44" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" t="s">
         <v>173</v>
       </c>
-      <c r="C44" t="s">
+      <c r="E44" t="s">
         <v>174</v>
-      </c>
-      <c r="D44" t="s">
-        <v>175</v>
-      </c>
-      <c r="E44" t="s">
-        <v>176</v>
       </c>
       <c r="F44" t="s">
         <v>42</v>
@@ -6581,16 +6572,16 @@
         <v>43</v>
       </c>
       <c r="I44" t="s">
+        <v>175</v>
+      </c>
+      <c r="J44" t="s">
+        <v>176</v>
+      </c>
+      <c r="K44" t="s">
         <v>177</v>
       </c>
-      <c r="J44" t="s">
+      <c r="L44" t="s">
         <v>178</v>
-      </c>
-      <c r="K44" t="s">
-        <v>179</v>
-      </c>
-      <c r="L44" t="s">
-        <v>180</v>
       </c>
       <c r="M44" t="s">
         <v>47</v>
@@ -6607,16 +6598,16 @@
         <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E45" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F45" t="s">
         <v>42</v>
@@ -6628,16 +6619,16 @@
         <v>43</v>
       </c>
       <c r="I45" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L45" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M45" t="s">
         <v>78</v>
@@ -6654,13 +6645,13 @@
         <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E46" t="s">
         <v>139</v>
@@ -6675,16 +6666,16 @@
         <v>43</v>
       </c>
       <c r="I46" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J46" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K46" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M46" t="s">
         <v>47</v>
@@ -6701,16 +6692,16 @@
         <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F47" t="s">
         <v>42</v>
@@ -6722,16 +6713,16 @@
         <v>43</v>
       </c>
       <c r="I47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J47" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M47" t="s">
         <v>47</v>
@@ -6748,13 +6739,13 @@
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D48" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E48" t="s">
         <v>139</v>
@@ -6769,16 +6760,16 @@
         <v>43</v>
       </c>
       <c r="I48" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J48" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K48" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M48" t="s">
         <v>47</v>
@@ -6795,16 +6786,16 @@
         <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E49" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F49" t="s">
         <v>42</v>
@@ -6816,16 +6807,16 @@
         <v>43</v>
       </c>
       <c r="I49" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J49" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K49" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L49" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M49" t="s">
         <v>47</v>
@@ -6842,13 +6833,13 @@
         <v>19</v>
       </c>
       <c r="B50" t="s">
+        <v>194</v>
+      </c>
+      <c r="C50" t="s">
+        <v>195</v>
+      </c>
+      <c r="D50" t="s">
         <v>196</v>
-      </c>
-      <c r="C50" t="s">
-        <v>197</v>
-      </c>
-      <c r="D50" t="s">
-        <v>198</v>
       </c>
       <c r="E50" t="s">
         <v>54</v>
@@ -6863,16 +6854,16 @@
         <v>43</v>
       </c>
       <c r="I50" t="s">
+        <v>197</v>
+      </c>
+      <c r="J50" t="s">
+        <v>198</v>
+      </c>
+      <c r="K50" t="s">
         <v>199</v>
       </c>
-      <c r="J50" t="s">
+      <c r="L50" t="s">
         <v>200</v>
-      </c>
-      <c r="K50" t="s">
-        <v>201</v>
-      </c>
-      <c r="L50" t="s">
-        <v>202</v>
       </c>
       <c r="M50" t="s">
         <v>47</v>
@@ -6889,13 +6880,13 @@
         <v>19</v>
       </c>
       <c r="B51" t="s">
+        <v>194</v>
+      </c>
+      <c r="C51" t="s">
+        <v>195</v>
+      </c>
+      <c r="D51" t="s">
         <v>196</v>
-      </c>
-      <c r="C51" t="s">
-        <v>197</v>
-      </c>
-      <c r="D51" t="s">
-        <v>198</v>
       </c>
       <c r="E51" t="s">
         <v>58</v>
@@ -6910,16 +6901,16 @@
         <v>43</v>
       </c>
       <c r="I51" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J51" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K51" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L51" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M51" t="s">
         <v>47</v>
@@ -6936,13 +6927,13 @@
         <v>19</v>
       </c>
       <c r="B52" t="s">
+        <v>194</v>
+      </c>
+      <c r="C52" t="s">
+        <v>195</v>
+      </c>
+      <c r="D52" t="s">
         <v>196</v>
-      </c>
-      <c r="C52" t="s">
-        <v>197</v>
-      </c>
-      <c r="D52" t="s">
-        <v>198</v>
       </c>
       <c r="E52" t="s">
         <v>72</v>
@@ -6957,16 +6948,16 @@
         <v>43</v>
       </c>
       <c r="I52" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J52" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K52" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L52" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M52" t="s">
         <v>78</v>
@@ -6983,13 +6974,13 @@
         <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C53" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D53" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E53" t="s">
         <v>58</v>
@@ -7004,16 +6995,16 @@
         <v>43</v>
       </c>
       <c r="I53" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J53" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K53" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M53" t="s">
         <v>47</v>
@@ -7030,16 +7021,16 @@
         <v>19</v>
       </c>
       <c r="B54" t="s">
+        <v>207</v>
+      </c>
+      <c r="C54" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" t="s">
         <v>209</v>
       </c>
-      <c r="C54" t="s">
+      <c r="E54" t="s">
         <v>210</v>
-      </c>
-      <c r="D54" t="s">
-        <v>211</v>
-      </c>
-      <c r="E54" t="s">
-        <v>212</v>
       </c>
       <c r="F54" t="s">
         <v>42</v>
@@ -7051,16 +7042,16 @@
         <v>43</v>
       </c>
       <c r="I54" t="s">
+        <v>211</v>
+      </c>
+      <c r="J54" t="s">
+        <v>212</v>
+      </c>
+      <c r="K54" t="s">
         <v>213</v>
       </c>
-      <c r="J54" t="s">
+      <c r="L54" t="s">
         <v>214</v>
-      </c>
-      <c r="K54" t="s">
-        <v>215</v>
-      </c>
-      <c r="L54" t="s">
-        <v>216</v>
       </c>
       <c r="M54" t="s">
         <v>47</v>
@@ -7077,16 +7068,16 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D55" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F55" t="s">
         <v>42</v>
@@ -7098,16 +7089,16 @@
         <v>43</v>
       </c>
       <c r="I55" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J55" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K55" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M55" t="s">
         <v>78</v>
@@ -7124,10 +7115,10 @@
         <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C56" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D56" t="s">
         <v>40</v>
@@ -7142,16 +7133,16 @@
         <v>1</v>
       </c>
       <c r="H56" t="s">
+        <v>221</v>
+      </c>
+      <c r="I56" t="s">
+        <v>222</v>
+      </c>
+      <c r="J56" t="s">
         <v>223</v>
       </c>
-      <c r="I56" t="s">
+      <c r="K56" t="s">
         <v>224</v>
-      </c>
-      <c r="J56" t="s">
-        <v>225</v>
-      </c>
-      <c r="K56" t="s">
-        <v>226</v>
       </c>
       <c r="L56" t="s">
         <v>43</v>
@@ -7171,10 +7162,10 @@
         <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C57" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D57" t="s">
         <v>60</v>
@@ -7189,16 +7180,16 @@
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I57" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J57" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K57" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L57" t="s">
         <v>43</v>
@@ -7218,10 +7209,10 @@
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D58" t="s">
         <v>67</v>
@@ -7239,16 +7230,16 @@
         <v>43</v>
       </c>
       <c r="I58" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J58" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K58" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L58" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M58" t="s">
         <v>47</v>
@@ -7265,16 +7256,16 @@
         <v>15</v>
       </c>
       <c r="B59" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59" t="s">
         <v>231</v>
       </c>
-      <c r="C59" t="s">
+      <c r="E59" t="s">
         <v>232</v>
-      </c>
-      <c r="D59" t="s">
-        <v>233</v>
-      </c>
-      <c r="E59" t="s">
-        <v>234</v>
       </c>
       <c r="F59" t="s">
         <v>158</v>
@@ -7283,16 +7274,16 @@
         <v>1</v>
       </c>
       <c r="H59" t="s">
+        <v>233</v>
+      </c>
+      <c r="I59" t="s">
+        <v>234</v>
+      </c>
+      <c r="J59" t="s">
         <v>235</v>
       </c>
-      <c r="I59" t="s">
-        <v>236</v>
-      </c>
-      <c r="J59" t="s">
-        <v>237</v>
-      </c>
       <c r="K59" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s">
         <v>43</v>
@@ -7312,16 +7303,16 @@
         <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C60" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D60" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E60" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F60" t="s">
         <v>158</v>
@@ -7330,16 +7321,16 @@
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J60" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K60" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L60" t="s">
         <v>43</v>
@@ -7359,16 +7350,16 @@
         <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C61" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D61" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F61" t="s">
         <v>158</v>
@@ -7377,16 +7368,16 @@
         <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I61" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J61" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K61" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L61" t="s">
         <v>43</v>
@@ -7406,16 +7397,16 @@
         <v>15</v>
       </c>
       <c r="B62" t="s">
+        <v>244</v>
+      </c>
+      <c r="C62" t="s">
+        <v>245</v>
+      </c>
+      <c r="D62" t="s">
         <v>246</v>
       </c>
-      <c r="C62" t="s">
-        <v>247</v>
-      </c>
-      <c r="D62" t="s">
-        <v>248</v>
-      </c>
       <c r="E62" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F62" t="s">
         <v>158</v>
@@ -7424,16 +7415,16 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
+        <v>247</v>
+      </c>
+      <c r="I62" t="s">
+        <v>248</v>
+      </c>
+      <c r="J62" t="s">
         <v>249</v>
       </c>
-      <c r="I62" t="s">
-        <v>250</v>
-      </c>
-      <c r="J62" t="s">
-        <v>251</v>
-      </c>
       <c r="K62" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L62" t="s">
         <v>43</v>
@@ -7453,16 +7444,16 @@
         <v>15</v>
       </c>
       <c r="B63" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C63" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D63" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E63" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F63" t="s">
         <v>158</v>
@@ -7471,16 +7462,16 @@
         <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I63" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J63" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K63" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L63" t="s">
         <v>43</v>
@@ -7500,16 +7491,16 @@
         <v>15</v>
       </c>
       <c r="B64" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D64" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E64" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F64" t="s">
         <v>158</v>
@@ -7518,16 +7509,16 @@
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I64" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J64" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K64" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L64" t="s">
         <v>43</v>
@@ -7547,16 +7538,16 @@
         <v>15</v>
       </c>
       <c r="B65" t="s">
+        <v>256</v>
+      </c>
+      <c r="C65" t="s">
+        <v>257</v>
+      </c>
+      <c r="D65" t="s">
         <v>258</v>
       </c>
-      <c r="C65" t="s">
+      <c r="E65" t="s">
         <v>259</v>
-      </c>
-      <c r="D65" t="s">
-        <v>260</v>
-      </c>
-      <c r="E65" t="s">
-        <v>261</v>
       </c>
       <c r="F65" t="s">
         <v>158</v>
@@ -7565,16 +7556,16 @@
         <v>1</v>
       </c>
       <c r="H65" t="s">
+        <v>260</v>
+      </c>
+      <c r="I65" t="s">
+        <v>261</v>
+      </c>
+      <c r="J65" t="s">
         <v>262</v>
       </c>
-      <c r="I65" t="s">
-        <v>263</v>
-      </c>
-      <c r="J65" t="s">
-        <v>264</v>
-      </c>
       <c r="K65" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L65" t="s">
         <v>43</v>
@@ -7594,16 +7585,16 @@
         <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D66" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E66" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F66" t="s">
         <v>158</v>
@@ -7612,16 +7603,16 @@
         <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I66" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J66" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K66" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L66" t="s">
         <v>43</v>
@@ -7641,16 +7632,16 @@
         <v>15</v>
       </c>
       <c r="B67" t="s">
+        <v>267</v>
+      </c>
+      <c r="C67" t="s">
+        <v>268</v>
+      </c>
+      <c r="D67" t="s">
         <v>269</v>
       </c>
-      <c r="C67" t="s">
-        <v>270</v>
-      </c>
-      <c r="D67" t="s">
-        <v>271</v>
-      </c>
       <c r="E67" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F67" t="s">
         <v>158</v>
@@ -7659,16 +7650,16 @@
         <v>3</v>
       </c>
       <c r="H67" t="s">
+        <v>270</v>
+      </c>
+      <c r="I67" t="s">
+        <v>271</v>
+      </c>
+      <c r="J67" t="s">
         <v>272</v>
       </c>
-      <c r="I67" t="s">
-        <v>273</v>
-      </c>
-      <c r="J67" t="s">
-        <v>274</v>
-      </c>
       <c r="K67" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L67" t="s">
         <v>43</v>
@@ -7688,16 +7679,16 @@
         <v>15</v>
       </c>
       <c r="B68" t="s">
+        <v>273</v>
+      </c>
+      <c r="C68" t="s">
+        <v>274</v>
+      </c>
+      <c r="D68" t="s">
         <v>275</v>
       </c>
-      <c r="C68" t="s">
-        <v>276</v>
-      </c>
-      <c r="D68" t="s">
-        <v>277</v>
-      </c>
       <c r="E68" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F68" t="s">
         <v>158</v>
@@ -7706,16 +7697,16 @@
         <v>1</v>
       </c>
       <c r="H68" t="s">
+        <v>276</v>
+      </c>
+      <c r="I68" t="s">
+        <v>277</v>
+      </c>
+      <c r="J68" t="s">
         <v>278</v>
       </c>
-      <c r="I68" t="s">
-        <v>279</v>
-      </c>
-      <c r="J68" t="s">
-        <v>280</v>
-      </c>
       <c r="K68" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L68" t="s">
         <v>43</v>
@@ -7735,16 +7726,16 @@
         <v>15</v>
       </c>
       <c r="B69" t="s">
+        <v>279</v>
+      </c>
+      <c r="C69" t="s">
+        <v>280</v>
+      </c>
+      <c r="D69" t="s">
         <v>281</v>
       </c>
-      <c r="C69" t="s">
-        <v>282</v>
-      </c>
-      <c r="D69" t="s">
-        <v>283</v>
-      </c>
       <c r="E69" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F69" t="s">
         <v>158</v>
@@ -7753,16 +7744,16 @@
         <v>1</v>
       </c>
       <c r="H69" t="s">
+        <v>282</v>
+      </c>
+      <c r="I69" t="s">
+        <v>283</v>
+      </c>
+      <c r="J69" t="s">
         <v>284</v>
       </c>
-      <c r="I69" t="s">
-        <v>285</v>
-      </c>
-      <c r="J69" t="s">
-        <v>286</v>
-      </c>
       <c r="K69" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L69" t="s">
         <v>43</v>
@@ -7782,16 +7773,16 @@
         <v>17</v>
       </c>
       <c r="B70" t="s">
+        <v>285</v>
+      </c>
+      <c r="C70" t="s">
+        <v>286</v>
+      </c>
+      <c r="D70" t="s">
         <v>287</v>
       </c>
-      <c r="C70" t="s">
+      <c r="E70" t="s">
         <v>288</v>
-      </c>
-      <c r="D70" t="s">
-        <v>289</v>
-      </c>
-      <c r="E70" t="s">
-        <v>290</v>
       </c>
       <c r="F70" t="s">
         <v>158</v>
@@ -7800,16 +7791,16 @@
         <v>1</v>
       </c>
       <c r="H70" t="s">
+        <v>289</v>
+      </c>
+      <c r="I70" t="s">
+        <v>290</v>
+      </c>
+      <c r="J70" t="s">
         <v>291</v>
       </c>
-      <c r="I70" t="s">
-        <v>292</v>
-      </c>
-      <c r="J70" t="s">
-        <v>293</v>
-      </c>
       <c r="K70" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L70" t="s">
         <v>43</v>
@@ -7829,16 +7820,16 @@
         <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C71" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D71" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E71" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F71" t="s">
         <v>158</v>
@@ -7847,16 +7838,16 @@
         <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I71" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J71" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K71" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L71" t="s">
         <v>43</v>
@@ -7876,16 +7867,16 @@
         <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C72" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D72" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E72" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F72" t="s">
         <v>158</v>
@@ -7894,16 +7885,16 @@
         <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I72" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J72" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K72" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L72" t="s">
         <v>43</v>
@@ -7923,16 +7914,16 @@
         <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C73" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D73" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E73" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F73" t="s">
         <v>158</v>
@@ -7941,16 +7932,16 @@
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I73" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J73" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L73" t="s">
         <v>43</v>
@@ -7970,16 +7961,16 @@
         <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C74" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D74" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E74" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F74" t="s">
         <v>158</v>
@@ -7988,16 +7979,16 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I74" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J74" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K74" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L74" t="s">
         <v>43</v>
@@ -8017,16 +8008,16 @@
         <v>17</v>
       </c>
       <c r="B75" t="s">
+        <v>308</v>
+      </c>
+      <c r="C75" t="s">
+        <v>309</v>
+      </c>
+      <c r="D75" t="s">
         <v>310</v>
       </c>
-      <c r="C75" t="s">
+      <c r="E75" t="s">
         <v>311</v>
-      </c>
-      <c r="D75" t="s">
-        <v>312</v>
-      </c>
-      <c r="E75" t="s">
-        <v>313</v>
       </c>
       <c r="F75" t="s">
         <v>158</v>
@@ -8035,16 +8026,16 @@
         <v>1</v>
       </c>
       <c r="H75" t="s">
+        <v>312</v>
+      </c>
+      <c r="I75" t="s">
+        <v>313</v>
+      </c>
+      <c r="J75" t="s">
         <v>314</v>
       </c>
-      <c r="I75" t="s">
-        <v>315</v>
-      </c>
-      <c r="J75" t="s">
-        <v>316</v>
-      </c>
       <c r="K75" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L75" t="s">
         <v>43</v>
@@ -8064,16 +8055,16 @@
         <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C76" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D76" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E76" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F76" t="s">
         <v>158</v>
@@ -8082,16 +8073,16 @@
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I76" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J76" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K76" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L76" t="s">
         <v>43</v>
@@ -8111,16 +8102,16 @@
         <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C77" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D77" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E77" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F77" t="s">
         <v>158</v>
@@ -8129,16 +8120,16 @@
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I77" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J77" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K77" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L77" t="s">
         <v>43</v>
@@ -8158,16 +8149,16 @@
         <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C78" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D78" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E78" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F78" t="s">
         <v>158</v>
@@ -8176,16 +8167,16 @@
         <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I78" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J78" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K78" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L78" t="s">
         <v>43</v>
@@ -8205,16 +8196,16 @@
         <v>17</v>
       </c>
       <c r="B79" t="s">
+        <v>327</v>
+      </c>
+      <c r="C79" t="s">
+        <v>328</v>
+      </c>
+      <c r="D79" t="s">
         <v>329</v>
       </c>
-      <c r="C79" t="s">
+      <c r="E79" t="s">
         <v>330</v>
-      </c>
-      <c r="D79" t="s">
-        <v>331</v>
-      </c>
-      <c r="E79" t="s">
-        <v>332</v>
       </c>
       <c r="F79" t="s">
         <v>158</v>
@@ -8223,16 +8214,16 @@
         <v>1</v>
       </c>
       <c r="H79" t="s">
+        <v>331</v>
+      </c>
+      <c r="I79" t="s">
+        <v>332</v>
+      </c>
+      <c r="J79" t="s">
         <v>333</v>
       </c>
-      <c r="I79" t="s">
+      <c r="K79" t="s">
         <v>334</v>
-      </c>
-      <c r="J79" t="s">
-        <v>335</v>
-      </c>
-      <c r="K79" t="s">
-        <v>336</v>
       </c>
       <c r="L79" t="s">
         <v>43</v>
@@ -8252,16 +8243,16 @@
         <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C80" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E80" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F80" t="s">
         <v>158</v>
@@ -8270,16 +8261,16 @@
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I80" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J80" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="K80" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L80" t="s">
         <v>43</v>
@@ -8299,16 +8290,16 @@
         <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C81" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E81" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F81" t="s">
         <v>42</v>
@@ -8320,13 +8311,13 @@
         <v>43</v>
       </c>
       <c r="I81" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J81" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="K81" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L81" t="s">
         <v>43</v>
@@ -8346,16 +8337,16 @@
         <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C82" t="s">
         <v>43</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E82" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F82" t="s">
         <v>158</v>
@@ -8370,10 +8361,10 @@
         <v>43</v>
       </c>
       <c r="J82" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K82" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L82" t="s">
         <v>43</v>
@@ -8385,7 +8376,7 @@
         <v>43</v>
       </c>
       <c r="O82" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
@@ -8393,16 +8384,16 @@
         <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C83" t="s">
         <v>43</v>
       </c>
       <c r="D83" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E83" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F83" t="s">
         <v>158</v>
@@ -8417,10 +8408,10 @@
         <v>43</v>
       </c>
       <c r="J83" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K83" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L83" t="s">
         <v>43</v>
@@ -8432,7 +8423,7 @@
         <v>43</v>
       </c>
       <c r="O83" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
@@ -8440,16 +8431,16 @@
         <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C84" t="s">
         <v>43</v>
       </c>
       <c r="D84" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E84" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F84" t="s">
         <v>158</v>
@@ -8464,10 +8455,10 @@
         <v>43</v>
       </c>
       <c r="J84" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K84" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L84" t="s">
         <v>43</v>
@@ -8479,7 +8470,7 @@
         <v>43</v>
       </c>
       <c r="O84" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
@@ -8487,16 +8478,16 @@
         <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C85" t="s">
         <v>43</v>
       </c>
       <c r="D85" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E85" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F85" t="s">
         <v>42</v>
@@ -8511,10 +8502,10 @@
         <v>43</v>
       </c>
       <c r="J85" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K85" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L85" t="s">
         <v>43</v>
@@ -8523,10 +8514,10 @@
         <v>47</v>
       </c>
       <c r="N85" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="O85" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
@@ -8534,16 +8525,16 @@
         <v>17</v>
       </c>
       <c r="B86" t="s">
+        <v>352</v>
+      </c>
+      <c r="C86" t="s">
+        <v>353</v>
+      </c>
+      <c r="D86" t="s">
         <v>354</v>
       </c>
-      <c r="C86" t="s">
-        <v>355</v>
-      </c>
-      <c r="D86" t="s">
-        <v>356</v>
-      </c>
       <c r="E86" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F86" t="s">
         <v>42</v>
@@ -8555,16 +8546,16 @@
         <v>43</v>
       </c>
       <c r="I86" t="s">
+        <v>355</v>
+      </c>
+      <c r="J86" t="s">
+        <v>356</v>
+      </c>
+      <c r="K86" t="s">
+        <v>224</v>
+      </c>
+      <c r="L86" t="s">
         <v>357</v>
-      </c>
-      <c r="J86" t="s">
-        <v>358</v>
-      </c>
-      <c r="K86" t="s">
-        <v>226</v>
-      </c>
-      <c r="L86" t="s">
-        <v>359</v>
       </c>
       <c r="M86" t="s">
         <v>47</v>
@@ -8581,16 +8572,16 @@
         <v>17</v>
       </c>
       <c r="B87" t="s">
+        <v>358</v>
+      </c>
+      <c r="C87" t="s">
+        <v>359</v>
+      </c>
+      <c r="D87" t="s">
         <v>360</v>
       </c>
-      <c r="C87" t="s">
-        <v>361</v>
-      </c>
-      <c r="D87" t="s">
-        <v>362</v>
-      </c>
       <c r="E87" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F87" t="s">
         <v>158</v>
@@ -8599,16 +8590,16 @@
         <v>4</v>
       </c>
       <c r="H87" t="s">
+        <v>361</v>
+      </c>
+      <c r="I87" t="s">
+        <v>362</v>
+      </c>
+      <c r="J87" t="s">
         <v>363</v>
       </c>
-      <c r="I87" t="s">
-        <v>364</v>
-      </c>
-      <c r="J87" t="s">
-        <v>365</v>
-      </c>
       <c r="K87" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L87" t="s">
         <v>43</v>
@@ -8628,16 +8619,16 @@
         <v>17</v>
       </c>
       <c r="B88" t="s">
+        <v>364</v>
+      </c>
+      <c r="C88" t="s">
+        <v>365</v>
+      </c>
+      <c r="D88" t="s">
         <v>366</v>
       </c>
-      <c r="C88" t="s">
-        <v>367</v>
-      </c>
-      <c r="D88" t="s">
-        <v>368</v>
-      </c>
       <c r="E88" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F88" t="s">
         <v>158</v>
@@ -8646,16 +8637,16 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
+        <v>367</v>
+      </c>
+      <c r="I88" t="s">
+        <v>368</v>
+      </c>
+      <c r="J88" t="s">
         <v>369</v>
       </c>
-      <c r="I88" t="s">
-        <v>370</v>
-      </c>
-      <c r="J88" t="s">
-        <v>371</v>
-      </c>
       <c r="K88" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L88" t="s">
         <v>43</v>
@@ -8675,16 +8666,16 @@
         <v>21</v>
       </c>
       <c r="B89" t="s">
+        <v>370</v>
+      </c>
+      <c r="C89" t="s">
+        <v>371</v>
+      </c>
+      <c r="D89" t="s">
         <v>372</v>
       </c>
-      <c r="C89" t="s">
+      <c r="E89" t="s">
         <v>373</v>
-      </c>
-      <c r="D89" t="s">
-        <v>374</v>
-      </c>
-      <c r="E89" t="s">
-        <v>375</v>
       </c>
       <c r="F89" t="s">
         <v>158</v>
@@ -8693,16 +8684,16 @@
         <v>1</v>
       </c>
       <c r="H89" t="s">
+        <v>374</v>
+      </c>
+      <c r="I89" t="s">
+        <v>375</v>
+      </c>
+      <c r="J89" t="s">
         <v>376</v>
       </c>
-      <c r="I89" t="s">
-        <v>377</v>
-      </c>
-      <c r="J89" t="s">
-        <v>378</v>
-      </c>
       <c r="K89" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L89" t="s">
         <v>43</v>
@@ -8722,16 +8713,16 @@
         <v>21</v>
       </c>
       <c r="B90" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C90" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D90" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E90" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F90" t="s">
         <v>158</v>
@@ -8740,16 +8731,16 @@
         <v>2</v>
       </c>
       <c r="H90" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I90" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J90" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K90" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L90" t="s">
         <v>43</v>
@@ -8769,16 +8760,16 @@
         <v>21</v>
       </c>
       <c r="B91" t="s">
+        <v>381</v>
+      </c>
+      <c r="C91" t="s">
+        <v>382</v>
+      </c>
+      <c r="D91" t="s">
         <v>383</v>
       </c>
-      <c r="C91" t="s">
-        <v>384</v>
-      </c>
-      <c r="D91" t="s">
-        <v>385</v>
-      </c>
       <c r="E91" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F91" t="s">
         <v>158</v>
@@ -8787,16 +8778,16 @@
         <v>4</v>
       </c>
       <c r="H91" t="s">
+        <v>384</v>
+      </c>
+      <c r="I91" t="s">
+        <v>385</v>
+      </c>
+      <c r="J91" t="s">
         <v>386</v>
       </c>
-      <c r="I91" t="s">
-        <v>387</v>
-      </c>
-      <c r="J91" t="s">
-        <v>388</v>
-      </c>
       <c r="K91" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L91" t="s">
         <v>43</v>
@@ -8997,7 +8988,7 @@
         <v>148</v>
       </c>
       <c r="L2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="M2" t="s">
         <v>47</v>
@@ -9014,10 +9005,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D3" t="s">
         <v>40</v>
@@ -9032,16 +9023,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J3" t="s">
         <v>223</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>224</v>
-      </c>
-      <c r="J3" t="s">
-        <v>225</v>
-      </c>
-      <c r="K3" t="s">
-        <v>226</v>
       </c>
       <c r="L3" t="s">
         <v>43</v>
@@ -9061,10 +9052,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -9079,16 +9070,16 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L4" t="s">
         <v>43</v>
@@ -9108,16 +9099,16 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" t="s">
         <v>231</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>232</v>
-      </c>
-      <c r="D5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E5" t="s">
-        <v>234</v>
       </c>
       <c r="F5" t="s">
         <v>158</v>
@@ -9126,16 +9117,16 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J5" t="s">
         <v>235</v>
       </c>
-      <c r="I5" t="s">
-        <v>236</v>
-      </c>
-      <c r="J5" t="s">
-        <v>237</v>
-      </c>
       <c r="K5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L5" t="s">
         <v>43</v>
@@ -9155,16 +9146,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F6" t="s">
         <v>158</v>
@@ -9173,16 +9164,16 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L6" t="s">
         <v>43</v>
@@ -9202,16 +9193,16 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F7" t="s">
         <v>158</v>
@@ -9220,16 +9211,16 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L7" t="s">
         <v>43</v>
@@ -9249,16 +9240,16 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" t="s">
         <v>246</v>
       </c>
-      <c r="C8" t="s">
-        <v>247</v>
-      </c>
-      <c r="D8" t="s">
-        <v>248</v>
-      </c>
       <c r="E8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F8" t="s">
         <v>158</v>
@@ -9267,16 +9258,16 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
+        <v>247</v>
+      </c>
+      <c r="I8" t="s">
+        <v>248</v>
+      </c>
+      <c r="J8" t="s">
         <v>249</v>
       </c>
-      <c r="I8" t="s">
-        <v>250</v>
-      </c>
-      <c r="J8" t="s">
-        <v>251</v>
-      </c>
       <c r="K8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L8" t="s">
         <v>43</v>
@@ -9296,16 +9287,16 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F9" t="s">
         <v>158</v>
@@ -9314,16 +9305,16 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L9" t="s">
         <v>43</v>
@@ -9343,16 +9334,16 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F10" t="s">
         <v>158</v>
@@ -9361,16 +9352,16 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L10" t="s">
         <v>43</v>
@@ -9390,16 +9381,16 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D11" t="s">
         <v>258</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>259</v>
-      </c>
-      <c r="D11" t="s">
-        <v>260</v>
-      </c>
-      <c r="E11" t="s">
-        <v>261</v>
       </c>
       <c r="F11" t="s">
         <v>158</v>
@@ -9408,16 +9399,16 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
+        <v>260</v>
+      </c>
+      <c r="I11" t="s">
+        <v>261</v>
+      </c>
+      <c r="J11" t="s">
         <v>262</v>
       </c>
-      <c r="I11" t="s">
-        <v>263</v>
-      </c>
-      <c r="J11" t="s">
-        <v>264</v>
-      </c>
       <c r="K11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L11" t="s">
         <v>43</v>
@@ -9437,16 +9428,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F12" t="s">
         <v>158</v>
@@ -9455,16 +9446,16 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L12" t="s">
         <v>43</v>
@@ -9484,16 +9475,16 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" t="s">
         <v>269</v>
       </c>
-      <c r="C13" t="s">
-        <v>270</v>
-      </c>
-      <c r="D13" t="s">
-        <v>271</v>
-      </c>
       <c r="E13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F13" t="s">
         <v>158</v>
@@ -9502,16 +9493,16 @@
         <v>3</v>
       </c>
       <c r="H13" t="s">
+        <v>270</v>
+      </c>
+      <c r="I13" t="s">
+        <v>271</v>
+      </c>
+      <c r="J13" t="s">
         <v>272</v>
       </c>
-      <c r="I13" t="s">
-        <v>273</v>
-      </c>
-      <c r="J13" t="s">
-        <v>274</v>
-      </c>
       <c r="K13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L13" t="s">
         <v>43</v>
@@ -9531,16 +9522,16 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C14" t="s">
+        <v>274</v>
+      </c>
+      <c r="D14" t="s">
         <v>275</v>
       </c>
-      <c r="C14" t="s">
-        <v>276</v>
-      </c>
-      <c r="D14" t="s">
-        <v>277</v>
-      </c>
       <c r="E14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F14" t="s">
         <v>158</v>
@@ -9549,16 +9540,16 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
+        <v>276</v>
+      </c>
+      <c r="I14" t="s">
+        <v>277</v>
+      </c>
+      <c r="J14" t="s">
         <v>278</v>
       </c>
-      <c r="I14" t="s">
-        <v>279</v>
-      </c>
-      <c r="J14" t="s">
-        <v>280</v>
-      </c>
       <c r="K14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L14" t="s">
         <v>43</v>
@@ -9578,16 +9569,16 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" t="s">
         <v>281</v>
       </c>
-      <c r="C15" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" t="s">
-        <v>283</v>
-      </c>
       <c r="E15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F15" t="s">
         <v>158</v>
@@ -9596,16 +9587,16 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
+        <v>282</v>
+      </c>
+      <c r="I15" t="s">
+        <v>283</v>
+      </c>
+      <c r="J15" t="s">
         <v>284</v>
       </c>
-      <c r="I15" t="s">
-        <v>285</v>
-      </c>
-      <c r="J15" t="s">
-        <v>286</v>
-      </c>
       <c r="K15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L15" t="s">
         <v>43</v>
@@ -9625,16 +9616,16 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C16" t="s">
+        <v>286</v>
+      </c>
+      <c r="D16" t="s">
         <v>287</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>288</v>
-      </c>
-      <c r="D16" t="s">
-        <v>289</v>
-      </c>
-      <c r="E16" t="s">
-        <v>290</v>
       </c>
       <c r="F16" t="s">
         <v>158</v>
@@ -9643,16 +9634,16 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
+        <v>289</v>
+      </c>
+      <c r="I16" t="s">
+        <v>290</v>
+      </c>
+      <c r="J16" t="s">
         <v>291</v>
       </c>
-      <c r="I16" t="s">
-        <v>292</v>
-      </c>
-      <c r="J16" t="s">
-        <v>293</v>
-      </c>
       <c r="K16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L16" t="s">
         <v>43</v>
@@ -9672,16 +9663,16 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D17" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F17" t="s">
         <v>158</v>
@@ -9690,16 +9681,16 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I17" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K17" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L17" t="s">
         <v>43</v>
@@ -9719,16 +9710,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C18" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E18" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F18" t="s">
         <v>158</v>
@@ -9737,16 +9728,16 @@
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I18" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s">
         <v>43</v>
@@ -9766,16 +9757,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C19" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D19" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F19" t="s">
         <v>158</v>
@@ -9784,16 +9775,16 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I19" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J19" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s">
         <v>43</v>
@@ -9813,16 +9804,16 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D20" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F20" t="s">
         <v>158</v>
@@ -9831,16 +9822,16 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s">
         <v>43</v>
@@ -9860,16 +9851,16 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
+        <v>308</v>
+      </c>
+      <c r="C21" t="s">
+        <v>309</v>
+      </c>
+      <c r="D21" t="s">
         <v>310</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>311</v>
-      </c>
-      <c r="D21" t="s">
-        <v>312</v>
-      </c>
-      <c r="E21" t="s">
-        <v>313</v>
       </c>
       <c r="F21" t="s">
         <v>158</v>
@@ -9878,16 +9869,16 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
+        <v>312</v>
+      </c>
+      <c r="I21" t="s">
+        <v>313</v>
+      </c>
+      <c r="J21" t="s">
         <v>314</v>
       </c>
-      <c r="I21" t="s">
-        <v>315</v>
-      </c>
-      <c r="J21" t="s">
-        <v>316</v>
-      </c>
       <c r="K21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L21" t="s">
         <v>43</v>
@@ -9907,16 +9898,16 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C22" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F22" t="s">
         <v>158</v>
@@ -9925,16 +9916,16 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I22" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J22" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K22" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s">
         <v>43</v>
@@ -9954,16 +9945,16 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C23" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D23" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E23" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F23" t="s">
         <v>158</v>
@@ -9972,16 +9963,16 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I23" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J23" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K23" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s">
         <v>43</v>
@@ -10001,16 +9992,16 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C24" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D24" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E24" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F24" t="s">
         <v>158</v>
@@ -10019,16 +10010,16 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I24" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J24" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K24" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s">
         <v>43</v>
@@ -10048,16 +10039,16 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
+        <v>327</v>
+      </c>
+      <c r="C25" t="s">
+        <v>328</v>
+      </c>
+      <c r="D25" t="s">
         <v>329</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>330</v>
-      </c>
-      <c r="D25" t="s">
-        <v>331</v>
-      </c>
-      <c r="E25" t="s">
-        <v>332</v>
       </c>
       <c r="F25" t="s">
         <v>158</v>
@@ -10066,16 +10057,16 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
+        <v>331</v>
+      </c>
+      <c r="I25" t="s">
+        <v>332</v>
+      </c>
+      <c r="J25" t="s">
         <v>333</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>334</v>
-      </c>
-      <c r="J25" t="s">
-        <v>335</v>
-      </c>
-      <c r="K25" t="s">
-        <v>336</v>
       </c>
       <c r="L25" t="s">
         <v>43</v>
@@ -10095,16 +10086,16 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C26" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E26" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F26" t="s">
         <v>158</v>
@@ -10113,16 +10104,16 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I26" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="K26" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L26" t="s">
         <v>43</v>
@@ -10142,16 +10133,16 @@
         <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C27" t="s">
         <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E27" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F27" t="s">
         <v>158</v>
@@ -10166,10 +10157,10 @@
         <v>43</v>
       </c>
       <c r="J27" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K27" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L27" t="s">
         <v>43</v>
@@ -10181,7 +10172,7 @@
         <v>43</v>
       </c>
       <c r="O27" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -10189,16 +10180,16 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C28" t="s">
         <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E28" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F28" t="s">
         <v>158</v>
@@ -10213,10 +10204,10 @@
         <v>43</v>
       </c>
       <c r="J28" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K28" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L28" t="s">
         <v>43</v>
@@ -10228,7 +10219,7 @@
         <v>43</v>
       </c>
       <c r="O28" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -10236,16 +10227,16 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C29" t="s">
         <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E29" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F29" t="s">
         <v>158</v>
@@ -10260,10 +10251,10 @@
         <v>43</v>
       </c>
       <c r="J29" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K29" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s">
         <v>43</v>
@@ -10275,7 +10266,7 @@
         <v>43</v>
       </c>
       <c r="O29" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -10283,16 +10274,16 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
+        <v>358</v>
+      </c>
+      <c r="C30" t="s">
+        <v>359</v>
+      </c>
+      <c r="D30" t="s">
         <v>360</v>
       </c>
-      <c r="C30" t="s">
-        <v>361</v>
-      </c>
-      <c r="D30" t="s">
-        <v>362</v>
-      </c>
       <c r="E30" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F30" t="s">
         <v>158</v>
@@ -10301,16 +10292,16 @@
         <v>4</v>
       </c>
       <c r="H30" t="s">
+        <v>361</v>
+      </c>
+      <c r="I30" t="s">
+        <v>362</v>
+      </c>
+      <c r="J30" t="s">
         <v>363</v>
       </c>
-      <c r="I30" t="s">
-        <v>364</v>
-      </c>
-      <c r="J30" t="s">
-        <v>365</v>
-      </c>
       <c r="K30" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L30" t="s">
         <v>43</v>
@@ -10330,16 +10321,16 @@
         <v>17</v>
       </c>
       <c r="B31" t="s">
+        <v>364</v>
+      </c>
+      <c r="C31" t="s">
+        <v>365</v>
+      </c>
+      <c r="D31" t="s">
         <v>366</v>
       </c>
-      <c r="C31" t="s">
-        <v>367</v>
-      </c>
-      <c r="D31" t="s">
-        <v>368</v>
-      </c>
       <c r="E31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F31" t="s">
         <v>158</v>
@@ -10348,16 +10339,16 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
+        <v>367</v>
+      </c>
+      <c r="I31" t="s">
+        <v>368</v>
+      </c>
+      <c r="J31" t="s">
         <v>369</v>
       </c>
-      <c r="I31" t="s">
-        <v>370</v>
-      </c>
-      <c r="J31" t="s">
-        <v>371</v>
-      </c>
       <c r="K31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L31" t="s">
         <v>43</v>
@@ -10377,16 +10368,16 @@
         <v>21</v>
       </c>
       <c r="B32" t="s">
+        <v>370</v>
+      </c>
+      <c r="C32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D32" t="s">
         <v>372</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>373</v>
-      </c>
-      <c r="D32" t="s">
-        <v>374</v>
-      </c>
-      <c r="E32" t="s">
-        <v>375</v>
       </c>
       <c r="F32" t="s">
         <v>158</v>
@@ -10395,16 +10386,16 @@
         <v>1</v>
       </c>
       <c r="H32" t="s">
+        <v>374</v>
+      </c>
+      <c r="I32" t="s">
+        <v>375</v>
+      </c>
+      <c r="J32" t="s">
         <v>376</v>
       </c>
-      <c r="I32" t="s">
-        <v>377</v>
-      </c>
-      <c r="J32" t="s">
-        <v>378</v>
-      </c>
       <c r="K32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L32" t="s">
         <v>43</v>
@@ -10424,16 +10415,16 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C33" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D33" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E33" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F33" t="s">
         <v>158</v>
@@ -10442,16 +10433,16 @@
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I33" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J33" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K33" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L33" t="s">
         <v>43</v>
@@ -10471,16 +10462,16 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
+        <v>381</v>
+      </c>
+      <c r="C34" t="s">
+        <v>382</v>
+      </c>
+      <c r="D34" t="s">
         <v>383</v>
       </c>
-      <c r="C34" t="s">
-        <v>384</v>
-      </c>
-      <c r="D34" t="s">
-        <v>385</v>
-      </c>
       <c r="E34" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F34" t="s">
         <v>158</v>
@@ -10489,16 +10480,16 @@
         <v>4</v>
       </c>
       <c r="H34" t="s">
+        <v>384</v>
+      </c>
+      <c r="I34" t="s">
+        <v>385</v>
+      </c>
+      <c r="J34" t="s">
         <v>386</v>
       </c>
-      <c r="I34" t="s">
-        <v>387</v>
-      </c>
-      <c r="J34" t="s">
-        <v>388</v>
-      </c>
       <c r="K34" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L34" t="s">
         <v>43</v>
@@ -10544,43 +10535,43 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>394</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>398</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>400</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>35</v>
@@ -10594,25 +10585,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F2" t="s">
         <v>402</v>
-      </c>
-      <c r="E2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F2" t="s">
-        <v>404</v>
       </c>
       <c r="G2" t="s">
         <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I2" t="s">
         <v>40</v>
@@ -10641,25 +10632,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F3" t="s">
         <v>402</v>
-      </c>
-      <c r="E3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F3" t="s">
-        <v>404</v>
       </c>
       <c r="G3" t="s">
         <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I3" t="s">
         <v>40</v>
@@ -10688,25 +10679,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E4" t="s">
+        <v>401</v>
+      </c>
+      <c r="F4" t="s">
         <v>402</v>
-      </c>
-      <c r="E4" t="s">
-        <v>403</v>
-      </c>
-      <c r="F4" t="s">
-        <v>404</v>
       </c>
       <c r="G4" t="s">
         <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I4" t="s">
         <v>40</v>
@@ -10735,25 +10726,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E5" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5" t="s">
         <v>402</v>
-      </c>
-      <c r="E5" t="s">
-        <v>403</v>
-      </c>
-      <c r="F5" t="s">
-        <v>404</v>
       </c>
       <c r="G5" t="s">
         <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I5" t="s">
         <v>40</v>
@@ -10782,25 +10773,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F6" t="s">
         <v>402</v>
-      </c>
-      <c r="E6" t="s">
-        <v>403</v>
-      </c>
-      <c r="F6" t="s">
-        <v>404</v>
       </c>
       <c r="G6" t="s">
         <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I6" t="s">
         <v>40</v>
@@ -10829,25 +10820,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
+        <v>400</v>
+      </c>
+      <c r="E7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F7" t="s">
         <v>402</v>
-      </c>
-      <c r="E7" t="s">
-        <v>403</v>
-      </c>
-      <c r="F7" t="s">
-        <v>404</v>
       </c>
       <c r="G7" t="s">
         <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I7" t="s">
         <v>40</v>
@@ -10876,25 +10867,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" t="s">
+        <v>401</v>
+      </c>
+      <c r="F8" t="s">
         <v>402</v>
-      </c>
-      <c r="E8" t="s">
-        <v>403</v>
-      </c>
-      <c r="F8" t="s">
-        <v>404</v>
       </c>
       <c r="G8" t="s">
         <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I8" t="s">
         <v>60</v>
@@ -10923,25 +10914,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E9" t="s">
+        <v>401</v>
+      </c>
+      <c r="F9" t="s">
         <v>402</v>
-      </c>
-      <c r="E9" t="s">
-        <v>403</v>
-      </c>
-      <c r="F9" t="s">
-        <v>404</v>
       </c>
       <c r="G9" t="s">
         <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I9" t="s">
         <v>60</v>
@@ -10970,25 +10961,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
+        <v>400</v>
+      </c>
+      <c r="E10" t="s">
+        <v>401</v>
+      </c>
+      <c r="F10" t="s">
         <v>402</v>
-      </c>
-      <c r="E10" t="s">
-        <v>403</v>
-      </c>
-      <c r="F10" t="s">
-        <v>404</v>
       </c>
       <c r="G10" t="s">
         <v>39</v>
       </c>
       <c r="H10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I10" t="s">
         <v>60</v>
@@ -11017,25 +11008,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11" t="s">
+        <v>400</v>
+      </c>
+      <c r="E11" t="s">
+        <v>401</v>
+      </c>
+      <c r="F11" t="s">
         <v>402</v>
-      </c>
-      <c r="E11" t="s">
-        <v>403</v>
-      </c>
-      <c r="F11" t="s">
-        <v>404</v>
       </c>
       <c r="G11" t="s">
         <v>39</v>
       </c>
       <c r="H11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I11" t="s">
         <v>60</v>
@@ -11064,25 +11055,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E12" t="s">
+        <v>401</v>
+      </c>
+      <c r="F12" t="s">
         <v>402</v>
-      </c>
-      <c r="E12" t="s">
-        <v>403</v>
-      </c>
-      <c r="F12" t="s">
-        <v>404</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
       </c>
       <c r="H12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I12" t="s">
         <v>67</v>
@@ -11111,25 +11102,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
+        <v>400</v>
+      </c>
+      <c r="E13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F13" t="s">
         <v>402</v>
-      </c>
-      <c r="E13" t="s">
-        <v>403</v>
-      </c>
-      <c r="F13" t="s">
-        <v>404</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
       </c>
       <c r="H13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I13" t="s">
         <v>67</v>
@@ -11158,25 +11149,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14" t="s">
+        <v>400</v>
+      </c>
+      <c r="E14" t="s">
+        <v>401</v>
+      </c>
+      <c r="F14" t="s">
         <v>402</v>
-      </c>
-      <c r="E14" t="s">
-        <v>403</v>
-      </c>
-      <c r="F14" t="s">
-        <v>404</v>
       </c>
       <c r="G14" t="s">
         <v>39</v>
       </c>
       <c r="H14" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I14" t="s">
         <v>67</v>
@@ -11205,25 +11196,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
+        <v>400</v>
+      </c>
+      <c r="E15" t="s">
+        <v>401</v>
+      </c>
+      <c r="F15" t="s">
         <v>402</v>
-      </c>
-      <c r="E15" t="s">
-        <v>403</v>
-      </c>
-      <c r="F15" t="s">
-        <v>404</v>
       </c>
       <c r="G15" t="s">
         <v>39</v>
       </c>
       <c r="H15" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I15" t="s">
         <v>67</v>
@@ -11252,25 +11243,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E16" t="s">
+        <v>401</v>
+      </c>
+      <c r="F16" t="s">
         <v>402</v>
-      </c>
-      <c r="E16" t="s">
-        <v>403</v>
-      </c>
-      <c r="F16" t="s">
-        <v>404</v>
       </c>
       <c r="G16" t="s">
         <v>39</v>
       </c>
       <c r="H16" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I16" t="s">
         <v>67</v>
@@ -11299,25 +11290,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C17" t="s">
         <v>19</v>
       </c>
       <c r="D17" t="s">
+        <v>400</v>
+      </c>
+      <c r="E17" t="s">
+        <v>401</v>
+      </c>
+      <c r="F17" t="s">
         <v>402</v>
-      </c>
-      <c r="E17" t="s">
-        <v>403</v>
-      </c>
-      <c r="F17" t="s">
-        <v>404</v>
       </c>
       <c r="G17" t="s">
         <v>39</v>
       </c>
       <c r="H17" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I17" t="s">
         <v>67</v>
@@ -11346,25 +11337,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
       </c>
       <c r="D18" t="s">
+        <v>400</v>
+      </c>
+      <c r="E18" t="s">
+        <v>401</v>
+      </c>
+      <c r="F18" t="s">
         <v>402</v>
-      </c>
-      <c r="E18" t="s">
-        <v>403</v>
-      </c>
-      <c r="F18" t="s">
-        <v>404</v>
       </c>
       <c r="G18" t="s">
         <v>39</v>
       </c>
       <c r="H18" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I18" t="s">
         <v>67</v>
@@ -11419,43 +11410,43 @@
   <sheetData>
     <row r="1" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>392</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>398</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>400</v>
       </c>
       <c r="N1" s="6" t="s">
         <v>35</v>
@@ -11469,19 +11460,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F2" t="s">
         <v>402</v>
-      </c>
-      <c r="E2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F2" t="s">
-        <v>404</v>
       </c>
       <c r="G2" t="s">
         <v>103</v>
@@ -11490,7 +11481,7 @@
         <v>105</v>
       </c>
       <c r="I2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
@@ -11516,19 +11507,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
       </c>
       <c r="D3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E3" t="s">
+        <v>404</v>
+      </c>
+      <c r="F3" t="s">
         <v>402</v>
-      </c>
-      <c r="E3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F3" t="s">
-        <v>404</v>
       </c>
       <c r="G3" t="s">
         <v>103</v>
@@ -11537,7 +11528,7 @@
         <v>111</v>
       </c>
       <c r="I3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J3" t="s">
         <v>43</v>
@@ -11563,19 +11554,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
       <c r="D4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E4" t="s">
+        <v>404</v>
+      </c>
+      <c r="F4" t="s">
         <v>402</v>
-      </c>
-      <c r="E4" t="s">
-        <v>406</v>
-      </c>
-      <c r="F4" t="s">
-        <v>404</v>
       </c>
       <c r="G4" t="s">
         <v>103</v>
@@ -11584,7 +11575,7 @@
         <v>115</v>
       </c>
       <c r="I4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J4" t="s">
         <v>43</v>
@@ -11610,19 +11601,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E5" t="s">
+        <v>404</v>
+      </c>
+      <c r="F5" t="s">
         <v>402</v>
-      </c>
-      <c r="E5" t="s">
-        <v>406</v>
-      </c>
-      <c r="F5" t="s">
-        <v>404</v>
       </c>
       <c r="G5" t="s">
         <v>103</v>
@@ -11631,7 +11622,7 @@
         <v>118</v>
       </c>
       <c r="I5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J5" t="s">
         <v>43</v>
@@ -11657,28 +11648,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
       <c r="D6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E6" t="s">
+        <v>404</v>
+      </c>
+      <c r="F6" t="s">
         <v>402</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>406</v>
-      </c>
-      <c r="F6" t="s">
-        <v>404</v>
-      </c>
-      <c r="G6" t="s">
-        <v>408</v>
       </c>
       <c r="H6" t="s">
         <v>122</v>
       </c>
       <c r="I6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J6" t="s">
         <v>43</v>
@@ -11704,28 +11695,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
+        <v>400</v>
+      </c>
+      <c r="E7" t="s">
+        <v>404</v>
+      </c>
+      <c r="F7" t="s">
         <v>402</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>406</v>
-      </c>
-      <c r="F7" t="s">
-        <v>404</v>
-      </c>
-      <c r="G7" t="s">
-        <v>408</v>
       </c>
       <c r="H7" t="s">
         <v>125</v>
       </c>
       <c r="I7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J7" t="s">
         <v>43</v>
@@ -11751,28 +11742,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" t="s">
+        <v>404</v>
+      </c>
+      <c r="F8" t="s">
         <v>402</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>406</v>
-      </c>
-      <c r="F8" t="s">
-        <v>404</v>
-      </c>
-      <c r="G8" t="s">
-        <v>408</v>
       </c>
       <c r="H8" t="s">
         <v>128</v>
       </c>
       <c r="I8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J8" t="s">
         <v>43</v>
@@ -11798,28 +11789,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="D9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E9" t="s">
+        <v>404</v>
+      </c>
+      <c r="F9" t="s">
         <v>402</v>
       </c>
-      <c r="E9" t="s">
-        <v>406</v>
-      </c>
-      <c r="F9" t="s">
-        <v>404</v>
-      </c>
       <c r="G9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H9" t="s">
         <v>122</v>
       </c>
       <c r="I9" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J9" t="s">
         <v>43</v>
@@ -11845,28 +11836,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
+        <v>400</v>
+      </c>
+      <c r="E10" t="s">
+        <v>404</v>
+      </c>
+      <c r="F10" t="s">
         <v>402</v>
       </c>
-      <c r="E10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F10" t="s">
-        <v>404</v>
-      </c>
       <c r="G10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H10" t="s">
         <v>125</v>
       </c>
       <c r="I10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J10" t="s">
         <v>43</v>
@@ -11892,28 +11883,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" t="s">
+        <v>400</v>
+      </c>
+      <c r="E11" t="s">
+        <v>404</v>
+      </c>
+      <c r="F11" t="s">
         <v>402</v>
       </c>
-      <c r="E11" t="s">
-        <v>406</v>
-      </c>
-      <c r="F11" t="s">
-        <v>404</v>
-      </c>
       <c r="G11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H11" t="s">
         <v>135</v>
       </c>
       <c r="I11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J11" t="s">
         <v>43</v>
@@ -11939,28 +11930,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="D12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E12" t="s">
+        <v>404</v>
+      </c>
+      <c r="F12" t="s">
         <v>402</v>
       </c>
-      <c r="E12" t="s">
-        <v>406</v>
-      </c>
-      <c r="F12" t="s">
-        <v>404</v>
-      </c>
       <c r="G12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H12" t="s">
         <v>139</v>
       </c>
       <c r="I12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J12" t="s">
         <v>43</v>
@@ -12012,43 +12003,43 @@
   <sheetData>
     <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>392</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>394</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>25</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>400</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>35</v>
@@ -12062,25 +12053,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F2" t="s">
         <v>402</v>
-      </c>
-      <c r="E2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F2" t="s">
-        <v>404</v>
       </c>
       <c r="G2" t="s">
         <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I2" t="s">
         <v>84</v>
@@ -12109,25 +12100,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F3" t="s">
         <v>402</v>
-      </c>
-      <c r="E3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F3" t="s">
-        <v>404</v>
       </c>
       <c r="G3" t="s">
         <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I3" t="s">
         <v>84</v>
@@ -12156,25 +12147,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E4" t="s">
+        <v>401</v>
+      </c>
+      <c r="F4" t="s">
         <v>402</v>
-      </c>
-      <c r="E4" t="s">
-        <v>403</v>
-      </c>
-      <c r="F4" t="s">
-        <v>404</v>
       </c>
       <c r="G4" t="s">
         <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I4" t="s">
         <v>84</v>
@@ -12203,25 +12194,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E5" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5" t="s">
         <v>402</v>
-      </c>
-      <c r="E5" t="s">
-        <v>403</v>
-      </c>
-      <c r="F5" t="s">
-        <v>404</v>
       </c>
       <c r="G5" t="s">
         <v>83</v>
       </c>
       <c r="H5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I5" t="s">
         <v>84</v>
@@ -12250,25 +12241,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F6" t="s">
         <v>402</v>
-      </c>
-      <c r="E6" t="s">
-        <v>403</v>
-      </c>
-      <c r="F6" t="s">
-        <v>404</v>
       </c>
       <c r="G6" t="s">
         <v>83</v>
       </c>
       <c r="H6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I6" t="s">
         <v>67</v>
@@ -12297,25 +12288,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
+        <v>400</v>
+      </c>
+      <c r="E7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F7" t="s">
         <v>402</v>
-      </c>
-      <c r="E7" t="s">
-        <v>403</v>
-      </c>
-      <c r="F7" t="s">
-        <v>404</v>
       </c>
       <c r="G7" t="s">
         <v>83</v>
       </c>
       <c r="H7" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I7" t="s">
         <v>67</v>
@@ -12344,25 +12335,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" t="s">
+        <v>401</v>
+      </c>
+      <c r="F8" t="s">
         <v>402</v>
-      </c>
-      <c r="E8" t="s">
-        <v>403</v>
-      </c>
-      <c r="F8" t="s">
-        <v>404</v>
       </c>
       <c r="G8" t="s">
         <v>83</v>
       </c>
       <c r="H8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I8" t="s">
         <v>67</v>
@@ -12391,25 +12382,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E9" t="s">
+        <v>401</v>
+      </c>
+      <c r="F9" t="s">
         <v>402</v>
-      </c>
-      <c r="E9" t="s">
-        <v>403</v>
-      </c>
-      <c r="F9" t="s">
-        <v>404</v>
       </c>
       <c r="G9" t="s">
         <v>83</v>
       </c>
       <c r="H9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I9" t="s">
         <v>67</v>
@@ -12461,13 +12452,13 @@
   <sheetData>
     <row r="1" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>389</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>391</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>24</v>
@@ -12476,19 +12467,19 @@
         <v>25</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>26</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>398</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>400</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>35</v>
@@ -12502,16 +12493,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F2" t="s">
         <v>67</v>
@@ -12523,7 +12514,7 @@
         <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J2" t="s">
         <v>42</v>
@@ -12532,7 +12523,7 @@
         <v>47</v>
       </c>
       <c r="L2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -12540,28 +12531,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" t="s">
         <v>341</v>
-      </c>
-      <c r="H3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" t="s">
-        <v>343</v>
       </c>
       <c r="J3" t="s">
         <v>42</v>
@@ -12578,28 +12569,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
       <c r="D4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E4" t="s">
+        <v>353</v>
+      </c>
+      <c r="F4" t="s">
+        <v>349</v>
+      </c>
+      <c r="G4" t="s">
         <v>354</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
         <v>355</v>
-      </c>
-      <c r="F4" t="s">
-        <v>351</v>
-      </c>
-      <c r="G4" t="s">
-        <v>356</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s">
-        <v>357</v>
       </c>
       <c r="J4" t="s">
         <v>42</v>
@@ -12608,7 +12599,7 @@
         <v>47</v>
       </c>
       <c r="L4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -12616,7 +12607,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -12654,28 +12645,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" t="s">
         <v>162</v>
-      </c>
-      <c r="E6" t="s">
-        <v>163</v>
       </c>
       <c r="F6" t="s">
         <v>145</v>
       </c>
       <c r="G6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
         <v>164</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" t="s">
-        <v>165</v>
       </c>
       <c r="J6" t="s">
         <v>42</v>
@@ -12684,7 +12675,7 @@
         <v>47</v>
       </c>
       <c r="L6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -12692,28 +12683,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" t="s">
         <v>162</v>
-      </c>
-      <c r="E7" t="s">
-        <v>163</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
         <v>168</v>
-      </c>
-      <c r="H7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" t="s">
-        <v>169</v>
       </c>
       <c r="J7" t="s">
         <v>42</v>
@@ -12722,7 +12713,7 @@
         <v>47</v>
       </c>
       <c r="L7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -12730,28 +12721,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" t="s">
         <v>162</v>
-      </c>
-      <c r="E8" t="s">
-        <v>163</v>
       </c>
       <c r="F8" t="s">
         <v>157</v>
       </c>
       <c r="G8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H8" t="s">
         <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J8" t="s">
         <v>42</v>
@@ -12760,7 +12751,7 @@
         <v>47</v>
       </c>
       <c r="L8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -12791,34 +12782,34 @@
   <sheetData>
     <row r="1" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>389</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>391</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>398</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>400</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>35</v>
@@ -12829,31 +12820,31 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" t="s">
         <v>174</v>
       </c>
-      <c r="F2" t="s">
-        <v>176</v>
-      </c>
       <c r="G2" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="H2" t="s">
         <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J2" t="s">
         <v>42</v>
@@ -12862,36 +12853,36 @@
         <v>47</v>
       </c>
       <c r="L2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G3" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="H3" t="s">
         <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J3" t="s">
         <v>42</v>
@@ -12905,31 +12896,31 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F4" t="s">
         <v>139</v>
       </c>
       <c r="G4" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="H4" t="s">
         <v>43</v>
       </c>
       <c r="I4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J4" t="s">
         <v>42</v>
@@ -12938,36 +12929,36 @@
         <v>47</v>
       </c>
       <c r="L4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G5" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="H5" t="s">
         <v>43</v>
       </c>
       <c r="I5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J5" t="s">
         <v>42</v>
@@ -12976,36 +12967,36 @@
         <v>47</v>
       </c>
       <c r="L5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F6" t="s">
         <v>139</v>
       </c>
       <c r="G6" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="H6" t="s">
         <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J6" t="s">
         <v>42</v>
@@ -13019,31 +13010,31 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G7" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="H7" t="s">
         <v>43</v>
       </c>
       <c r="I7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J7" t="s">
         <v>42</v>
@@ -13057,31 +13048,31 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" t="s">
+        <v>403</v>
+      </c>
+      <c r="G8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" t="s">
         <v>197</v>
-      </c>
-      <c r="F8" t="s">
-        <v>405</v>
-      </c>
-      <c r="G8" t="s">
-        <v>197</v>
-      </c>
-      <c r="H8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" t="s">
-        <v>199</v>
       </c>
       <c r="J8" t="s">
         <v>42</v>
@@ -13090,36 +13081,36 @@
         <v>47</v>
       </c>
       <c r="L8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F9" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H9" t="s">
         <v>43</v>
       </c>
       <c r="I9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J9" t="s">
         <v>42</v>
@@ -13133,31 +13124,31 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H10" t="s">
         <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J10" t="s">
         <v>42</v>
@@ -13171,31 +13162,31 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H11" t="s">
         <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J11" t="s">
         <v>42</v>
@@ -13204,36 +13195,36 @@
         <v>47</v>
       </c>
       <c r="L11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H12" t="s">
         <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J12" t="s">
         <v>42</v>
@@ -13242,36 +13233,36 @@
         <v>47</v>
       </c>
       <c r="L12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H13" t="s">
         <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J13" t="s">
         <v>42</v>
@@ -13280,7 +13271,7 @@
         <v>78</v>
       </c>
       <c r="L13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
